--- a/NVDA.xlsx
+++ b/NVDA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{345E59E3-6029-44B8-B393-2D68C9214A7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED68820-CCFF-4A8E-BD07-1EC07BE30AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{A1D5ACA9-E4BA-4D51-A2F0-408DF60F7C0B}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{A1D5ACA9-E4BA-4D51-A2F0-408DF60F7C0B}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>NVIDIA</t>
   </si>
@@ -550,13 +550,19 @@
     <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -671,57 +677,61 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -1151,7 +1161,7 @@
         <v>3</v>
       </c>
       <c r="I2" s="12">
-        <v>217.23</v>
+        <v>222.97</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -1159,10 +1169,10 @@
         <v>4</v>
       </c>
       <c r="I3" s="4">
-        <v>24286</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>115</v>
+        <v>24100</v>
+      </c>
+      <c r="J3" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -1174,7 +1184,7 @@
       </c>
       <c r="I4" s="4">
         <f>I2*I3</f>
-        <v>5275647.7799999993</v>
+        <v>5373577</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -1185,23 +1195,22 @@
         <v>6</v>
       </c>
       <c r="I5" s="4">
-        <f>13237+37098+30237</f>
-        <v>80572</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>115</v>
+        <f>22443+34143</f>
+        <v>56586</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="H6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="26">
-        <f>7470+1000</f>
-        <v>8470</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>115</v>
+      <c r="I6" s="25">
+        <v>32366</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -1216,7 +1225,7 @@
       </c>
       <c r="I7" s="4">
         <f>I4-I5+I6</f>
-        <v>5203545.7799999993</v>
+        <v>5349357</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
@@ -1460,6 +1469,9 @@
       <c r="O3" s="4">
         <v>75246</v>
       </c>
+      <c r="P3" s="4">
+        <v>89023</v>
+      </c>
       <c r="AQ3" s="4">
         <v>15005</v>
       </c>
@@ -1517,7 +1529,10 @@
         <f t="shared" ref="N4:N14" si="2">+AT4-SUM(K4:M4)</f>
         <v>51334</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P4" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ4" s="4">
@@ -1577,7 +1592,10 @@
         <f t="shared" si="2"/>
         <v>10980</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="O5" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P5" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ5" s="4">
@@ -1595,38 +1613,56 @@
     </row>
     <row r="6" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>149</v>
       </c>
       <c r="K6" s="4">
         <v>17599</v>
       </c>
+      <c r="L6" s="4">
+        <v>24168</v>
+      </c>
       <c r="O6" s="4">
         <v>37869</v>
+      </c>
+      <c r="P6" s="4">
+        <v>48719</v>
       </c>
     </row>
     <row r="7" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>150</v>
       </c>
       <c r="K7" s="4">
         <v>21513</v>
       </c>
+      <c r="L7" s="4">
+        <v>16828</v>
+      </c>
       <c r="O7" s="4">
         <v>37377</v>
+      </c>
+      <c r="P7" s="4">
+        <v>40313</v>
       </c>
     </row>
     <row r="8" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>151</v>
       </c>
       <c r="K8" s="4">
         <v>4950</v>
       </c>
+      <c r="L8" s="4">
+        <v>5647</v>
+      </c>
       <c r="O8" s="4">
         <v>6369</v>
+      </c>
+      <c r="P8" s="4">
+        <v>7198</v>
       </c>
     </row>
     <row r="9" spans="1:71" s="4" customFormat="1" x14ac:dyDescent="0.2">
@@ -1673,7 +1709,10 @@
         <f t="shared" si="2"/>
         <v>3727</v>
       </c>
-      <c r="O9" s="28" t="s">
+      <c r="O9" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P9" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ9" s="4">
@@ -1733,7 +1772,10 @@
         <f t="shared" si="2"/>
         <v>1321</v>
       </c>
-      <c r="O10" s="28" t="s">
+      <c r="O10" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P10" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ10" s="4">
@@ -1793,7 +1835,10 @@
         <f t="shared" si="2"/>
         <v>604</v>
       </c>
-      <c r="O11" s="28" t="s">
+      <c r="O11" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P11" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ11" s="4">
@@ -1853,7 +1898,10 @@
         <f t="shared" si="2"/>
         <v>161</v>
       </c>
-      <c r="O12" s="28" t="s">
+      <c r="O12" s="27" t="s">
+        <v>152</v>
+      </c>
+      <c r="P12" s="27" t="s">
         <v>152</v>
       </c>
       <c r="AQ12" s="4">
@@ -1914,6 +1962,9 @@
       <c r="O13" s="4">
         <v>74550</v>
       </c>
+      <c r="P13" s="4">
+        <v>88299</v>
+      </c>
       <c r="AM13" s="4">
         <v>2932</v>
       </c>
@@ -1983,6 +2034,9 @@
       </c>
       <c r="O14" s="4">
         <v>7065</v>
+      </c>
+      <c r="P14" s="4">
+        <v>7922</v>
       </c>
       <c r="T14" s="21"/>
       <c r="U14" s="21"/>
@@ -2066,7 +2120,9 @@
       <c r="O15" s="8">
         <v>81615</v>
       </c>
-      <c r="P15" s="8"/>
+      <c r="P15" s="8">
+        <v>96221</v>
+      </c>
       <c r="Q15" s="8"/>
       <c r="R15" s="8"/>
       <c r="S15" s="8"/>
@@ -2208,6 +2264,9 @@
       <c r="O16" s="4">
         <v>20458</v>
       </c>
+      <c r="P16" s="4">
+        <v>24079</v>
+      </c>
       <c r="T16" s="4">
         <v>141.84299999999999</v>
       </c>
@@ -2329,7 +2388,7 @@
         <v>22574</v>
       </c>
       <c r="I17" s="4">
-        <f t="shared" ref="I17:O17" si="5">+I15-I16</f>
+        <f t="shared" ref="I17:P17" si="5">+I15-I16</f>
         <v>26156</v>
       </c>
       <c r="J17" s="4">
@@ -2355,6 +2414,10 @@
       <c r="O17" s="4">
         <f t="shared" si="5"/>
         <v>61157</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" si="5"/>
+        <v>72142</v>
       </c>
       <c r="T17" s="4">
         <f t="shared" ref="T17:Y17" si="6">+T15-T16</f>
@@ -2517,6 +2580,9 @@
       <c r="O18" s="4">
         <v>6321</v>
       </c>
+      <c r="P18" s="4">
+        <v>7054</v>
+      </c>
       <c r="W18" s="4">
         <v>224.87299999999999</v>
       </c>
@@ -2645,6 +2711,9 @@
       <c r="O19" s="4">
         <v>1300</v>
       </c>
+      <c r="P19" s="4">
+        <v>1354</v>
+      </c>
       <c r="W19" s="4">
         <v>151.48500000000001</v>
       </c>
@@ -2773,7 +2842,9 @@
       <c r="O20" s="18">
         <v>0</v>
       </c>
-      <c r="P20" s="18"/>
+      <c r="P20" s="18">
+        <v>0</v>
+      </c>
       <c r="Q20" s="18"/>
       <c r="R20" s="18"/>
       <c r="T20" s="4">
@@ -2921,7 +2992,7 @@
         <v>21869</v>
       </c>
       <c r="J21" s="4">
-        <f t="shared" ref="J21:O21" si="17">+J17-J18-J19-J20</f>
+        <f t="shared" ref="J21:P21" si="17">+J17-J18-J19-J20</f>
         <v>24033</v>
       </c>
       <c r="K21" s="4">
@@ -2943,6 +3014,10 @@
       <c r="O21" s="4">
         <f t="shared" si="17"/>
         <v>53536</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="17"/>
+        <v>63734</v>
       </c>
       <c r="T21" s="4">
         <f t="shared" ref="T21:AM21" si="18">+T17-T20</f>
@@ -3105,6 +3180,9 @@
       <c r="O22" s="4">
         <v>540</v>
       </c>
+      <c r="P22" s="4">
+        <v>0</v>
+      </c>
       <c r="T22" s="4">
         <v>23.245999999999999</v>
       </c>
@@ -3246,6 +3324,9 @@
       <c r="O23" s="4">
         <v>102</v>
       </c>
+      <c r="P23" s="29">
+        <v>0</v>
+      </c>
       <c r="T23" s="4">
         <f t="shared" ref="T23:AM23" si="20">+T21+T22</f>
         <v>255.90800000000002</v>
@@ -3403,6 +3484,9 @@
       <c r="O24" s="4">
         <v>15929</v>
       </c>
+      <c r="P24" s="4">
+        <v>7773</v>
+      </c>
       <c r="T24" s="4">
         <v>59.758000000000003</v>
       </c>
@@ -3524,7 +3608,7 @@
         <v>19214</v>
       </c>
       <c r="I25" s="4">
-        <f t="shared" ref="I25:O25" si="22">+I21+I22-I23+I24</f>
+        <f t="shared" ref="I25:P25" si="22">+I21+I22-I23+I24</f>
         <v>22316</v>
       </c>
       <c r="J25" s="4">
@@ -3550,6 +3634,10 @@
       <c r="O25" s="4">
         <f t="shared" si="22"/>
         <v>69903</v>
+      </c>
+      <c r="P25" s="4">
+        <f t="shared" si="22"/>
+        <v>71507</v>
       </c>
       <c r="T25" s="4">
         <f t="shared" ref="T25:AM25" si="23">+T23-T24</f>
@@ -3712,6 +3800,9 @@
       <c r="O26" s="4">
         <v>11582</v>
       </c>
+      <c r="P26" s="4">
+        <v>11819</v>
+      </c>
       <c r="T26" s="4">
         <v>1.1599999999999999</v>
       </c>
@@ -3833,7 +3924,7 @@
         <v>16599</v>
       </c>
       <c r="I27" s="4">
-        <f t="shared" ref="I27:O27" si="26">+I25-I26</f>
+        <f t="shared" ref="I27:P27" si="26">+I25-I26</f>
         <v>19309</v>
       </c>
       <c r="J27" s="4">
@@ -3859,6 +3950,10 @@
       <c r="O27" s="4">
         <f t="shared" si="26"/>
         <v>58321</v>
+      </c>
+      <c r="P27" s="4">
+        <f t="shared" si="26"/>
+        <v>59688</v>
       </c>
       <c r="T27" s="4">
         <v>168</v>
@@ -4083,7 +4178,7 @@
         <v>0.67536007811864274</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" ref="I29:O29" si="29">I27/I30</f>
+        <f t="shared" ref="I29:P29" si="29">I27/I30</f>
         <v>0.78706232421636169</v>
       </c>
       <c r="J29" s="10">
@@ -4110,7 +4205,10 @@
         <f t="shared" si="29"/>
         <v>2.4014246891213045</v>
       </c>
-      <c r="P29" s="10"/>
+      <c r="P29" s="10">
+        <f t="shared" si="29"/>
+        <v>2.4674658949979329</v>
+      </c>
       <c r="Q29" s="10"/>
       <c r="R29" s="10"/>
       <c r="S29" s="10"/>
@@ -4321,7 +4419,9 @@
       <c r="O30" s="4">
         <v>24286</v>
       </c>
-      <c r="P30" s="4"/>
+      <c r="P30" s="4">
+        <v>24190</v>
+      </c>
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
@@ -4568,42 +4668,45 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="9">
-        <f>G3/C3-1</f>
+        <f t="shared" ref="G32:P34" si="32">G3/C3-1</f>
         <v>4.2668067226890756</v>
       </c>
       <c r="H32" s="9">
-        <f>H3/D3-1</f>
+        <f t="shared" si="32"/>
         <v>1.5449966095127388</v>
       </c>
       <c r="I32" s="9">
-        <f>I3/E3-1</f>
+        <f t="shared" si="32"/>
         <v>1.1200909466721787</v>
       </c>
       <c r="J32" s="9">
-        <f>J3/F3-1</f>
+        <f t="shared" si="32"/>
         <v>0.93327537491849588</v>
       </c>
       <c r="K32" s="9">
-        <f>K3/G3-1</f>
+        <f t="shared" si="32"/>
         <v>0.73345743030625354</v>
       </c>
       <c r="L32" s="9">
-        <f>L3/H3-1</f>
+        <f t="shared" si="32"/>
         <v>0.56425091352009749</v>
       </c>
       <c r="M32" s="9">
-        <f>M3/I3-1</f>
+        <f t="shared" si="32"/>
         <v>0.66439179747164534</v>
       </c>
       <c r="N32" s="9">
-        <f>N3/J3-1</f>
+        <f t="shared" si="32"/>
         <v>0.75137717818999428</v>
       </c>
       <c r="O32" s="9">
-        <f>O3/K3-1</f>
+        <f t="shared" si="32"/>
         <v>0.92385968500715898</v>
       </c>
-      <c r="P32" s="9"/>
+      <c r="P32" s="9">
+        <f t="shared" si="32"/>
+        <v>1.166220556745182</v>
+      </c>
       <c r="Q32" s="9"/>
       <c r="R32" s="9"/>
       <c r="S32" s="9"/>
@@ -4696,42 +4799,43 @@
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="9">
-        <f>G4/C4-1</f>
+        <f t="shared" si="32"/>
         <v>4.7765862377122428</v>
       </c>
       <c r="H33" s="9">
-        <f>H4/D4-1</f>
+        <f t="shared" si="32"/>
         <v>1.6247097073850441</v>
       </c>
       <c r="I33" s="9">
-        <f>I4/E4-1</f>
+        <f t="shared" si="32"/>
         <v>1.321464561639234</v>
       </c>
       <c r="J33" s="9">
-        <f>J4/F4-1</f>
+        <f t="shared" si="32"/>
         <v>1.1598885424268559</v>
       </c>
       <c r="K33" s="9">
-        <f>K4/G4-1</f>
+        <f t="shared" si="32"/>
         <v>0.76129331683168311</v>
       </c>
       <c r="L33" s="9">
-        <f>L4/H4-1</f>
+        <f t="shared" si="32"/>
         <v>0.49725712263316235</v>
       </c>
       <c r="M33" s="9">
-        <f>M4/I4-1</f>
+        <f t="shared" si="32"/>
         <v>0.55650412386051218</v>
       </c>
       <c r="N33" s="9">
-        <f>N4/J4-1</f>
+        <f t="shared" si="32"/>
         <v>0.57679076053569234</v>
       </c>
-      <c r="O33" s="9" t="e">
-        <f>O4/K4-1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P33" s="9"/>
+      <c r="O33" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P33" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q33" s="9"/>
       <c r="R33" s="9"/>
       <c r="S33" s="9"/>
@@ -4761,11 +4865,11 @@
       <c r="AQ33" s="9"/>
       <c r="AR33" s="9"/>
       <c r="AS33" s="9">
-        <f>+AS3/AR3-1</f>
+        <f t="shared" ref="AS33:AT35" si="33">+AS3/AR3-1</f>
         <v>1.4236927932667016</v>
       </c>
       <c r="AT33" s="9">
-        <f>+AT3/AS3-1</f>
+        <f t="shared" si="33"/>
         <v>0.68194919521469632</v>
       </c>
       <c r="AU33" s="6"/>
@@ -4831,42 +4935,43 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="9">
-        <f>G5/C5-1</f>
+        <f t="shared" si="32"/>
         <v>2.4207119741100325</v>
       </c>
       <c r="H34" s="9">
-        <f>H5/D5-1</f>
+        <f t="shared" si="32"/>
         <v>1.1437755698421976</v>
       </c>
       <c r="I34" s="9">
-        <f>I5/E5-1</f>
+        <f t="shared" si="32"/>
         <v>0.19992325402916356</v>
       </c>
       <c r="J34" s="9">
-        <f>J5/F5-1</f>
+        <f t="shared" si="32"/>
         <v>-9.2164515160612415E-2</v>
       </c>
       <c r="K34" s="9">
-        <f>K5/G5-1</f>
+        <f t="shared" si="32"/>
         <v>0.56322926521602024</v>
       </c>
       <c r="L34" s="9">
-        <f>L5/H5-1</f>
+        <f t="shared" si="32"/>
         <v>0.97709923664122145</v>
       </c>
       <c r="M34" s="9">
-        <f>M5/I5-1</f>
+        <f t="shared" si="32"/>
         <v>1.618164374800128</v>
       </c>
       <c r="N34" s="9">
-        <f>N5/J5-1</f>
+        <f t="shared" si="32"/>
         <v>2.6309523809523809</v>
       </c>
-      <c r="O34" s="9" t="e">
-        <f>O5/K5-1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P34" s="9"/>
+      <c r="O34" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P34" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q34" s="9"/>
       <c r="R34" s="9"/>
       <c r="S34" s="9"/>
@@ -4896,11 +5001,11 @@
       <c r="AQ34" s="9"/>
       <c r="AR34" s="9"/>
       <c r="AS34" s="9">
-        <f>+AS4/AR4-1</f>
+        <f t="shared" si="33"/>
         <v>1.6237740693196407</v>
       </c>
       <c r="AT34" s="9">
-        <f>+AT4/AS4-1</f>
+        <f t="shared" si="33"/>
         <v>0.58872167208109905</v>
       </c>
       <c r="AU34" s="6"/>
@@ -4966,42 +5071,43 @@
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="9">
-        <f t="shared" ref="G35:N38" si="32">G9/C9-1</f>
+        <f t="shared" ref="G35:N38" si="34">G9/C9-1</f>
         <v>0.18169642857142865</v>
       </c>
       <c r="H35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.15848753016894612</v>
       </c>
       <c r="I35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.14810924369747891</v>
       </c>
       <c r="J35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>-0.11204188481675392</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.42160936909709101</v>
       </c>
       <c r="L35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.48854166666666665</v>
       </c>
       <c r="M35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.30070143336383048</v>
       </c>
       <c r="N35" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.46501572327044016</v>
       </c>
-      <c r="O35" s="9" t="e">
-        <f t="shared" ref="O35:O38" si="33">O9/K9-1</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P35" s="9"/>
+      <c r="O35" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P35" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
       <c r="S35" s="9"/>
@@ -5031,11 +5137,11 @@
       <c r="AQ35" s="9"/>
       <c r="AR35" s="9"/>
       <c r="AS35" s="9">
-        <f>+AS5/AR5-1</f>
+        <f t="shared" si="33"/>
         <v>0.51486880466472296</v>
       </c>
       <c r="AT35" s="9">
-        <f>+AT5/AS5-1</f>
+        <f t="shared" si="33"/>
         <v>1.4153964588144725</v>
       </c>
       <c r="AU35" s="6"/>
@@ -5101,42 +5207,43 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.44745762711864412</v>
       </c>
       <c r="H36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.19788918205804751</v>
       </c>
       <c r="I36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.16826923076923084</v>
       </c>
       <c r="J36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.10367170626349886</v>
       </c>
       <c r="K36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.19203747072599531</v>
       </c>
       <c r="L36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.32378854625550657</v>
       </c>
       <c r="M36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.56378600823045266</v>
       </c>
       <c r="N36" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.5851272015655575</v>
       </c>
-      <c r="O36" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P36" s="9"/>
+      <c r="O36" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P36" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q36" s="9"/>
       <c r="R36" s="9"/>
       <c r="S36" s="9"/>
@@ -5166,11 +5273,11 @@
       <c r="AQ36" s="9"/>
       <c r="AR36" s="9"/>
       <c r="AS36" s="9">
-        <f t="shared" ref="AS36:AT38" si="34">+AS9/AR9-1</f>
+        <f t="shared" ref="AS36:AT38" si="35">+AS9/AR9-1</f>
         <v>8.643629750167503E-2</v>
       </c>
       <c r="AT36" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.41339207048458149</v>
       </c>
       <c r="AU36" s="6"/>
@@ -5236,42 +5343,43 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.1114864864864864</v>
       </c>
       <c r="H37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.3359073359073359</v>
       </c>
       <c r="I37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.72030651340996177</v>
       </c>
       <c r="J37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.0727272727272728</v>
       </c>
       <c r="K37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.72340425531914887</v>
       </c>
       <c r="L37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.69364161849710992</v>
       </c>
       <c r="M37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.31848552338530056</v>
       </c>
       <c r="N37" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>5.9649122807017507E-2</v>
       </c>
-      <c r="O37" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P37" s="9"/>
+      <c r="O37" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P37" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
       <c r="S37" s="9"/>
@@ -5301,11 +5409,11 @@
       <c r="AQ37" s="9"/>
       <c r="AR37" s="9"/>
       <c r="AS37" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.20927237604636195</v>
       </c>
       <c r="AT37" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.6991480298189563</v>
       </c>
       <c r="AU37" s="6"/>
@@ -5371,42 +5479,43 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>1.298701298701288E-2</v>
       </c>
       <c r="H38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.33333333333333326</v>
       </c>
       <c r="I38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.32876712328767121</v>
       </c>
       <c r="J38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.39999999999999991</v>
       </c>
       <c r="K38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.42307692307692313</v>
       </c>
       <c r="L38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.96590909090909083</v>
       </c>
       <c r="M38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.79381443298969079</v>
       </c>
       <c r="N38" s="9">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>0.27777777777777768</v>
       </c>
-      <c r="O38" s="9" t="e">
-        <f t="shared" si="33"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="P38" s="9"/>
+      <c r="O38" s="30" t="s">
+        <v>152</v>
+      </c>
+      <c r="P38" s="30" t="s">
+        <v>152</v>
+      </c>
       <c r="Q38" s="9"/>
       <c r="R38" s="9"/>
       <c r="S38" s="9"/>
@@ -5436,11 +5545,11 @@
       <c r="AQ38" s="9"/>
       <c r="AR38" s="9"/>
       <c r="AS38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.55270394133822176</v>
       </c>
       <c r="AT38" s="9">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>0.38665879574970474</v>
       </c>
       <c r="AU38" s="6"/>
@@ -5506,140 +5615,143 @@
       <c r="E39" s="8"/>
       <c r="F39" s="8"/>
       <c r="G39" s="11">
-        <f t="shared" ref="G39" si="35">G15/C15-1</f>
+        <f t="shared" ref="G39" si="36">G15/C15-1</f>
         <v>2.6212458286985538</v>
       </c>
       <c r="H39" s="11">
-        <f t="shared" ref="H39" si="36">H15/D15-1</f>
+        <f t="shared" ref="H39" si="37">H15/D15-1</f>
         <v>1.2240319834160065</v>
       </c>
       <c r="I39" s="11">
-        <f t="shared" ref="I39:N39" si="37">I15/E15-1</f>
+        <f t="shared" ref="I39:N39" si="38">I15/E15-1</f>
         <v>0.93609271523178816</v>
       </c>
       <c r="J39" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.77944170474596208</v>
       </c>
       <c r="K39" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.69182921210259551</v>
       </c>
       <c r="L39" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.5560252996005326</v>
       </c>
       <c r="M39" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.62493586454592109</v>
       </c>
       <c r="N39" s="11">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>0.73214512725331171</v>
       </c>
       <c r="O39" s="11">
-        <f t="shared" ref="O39" si="38">O15/K15-1</f>
+        <f t="shared" ref="O39:P39" si="39">O15/K15-1</f>
         <v>0.85227633788752222</v>
       </c>
-      <c r="P39" s="11"/>
+      <c r="P39" s="11">
+        <f t="shared" si="39"/>
+        <v>1.0585114348672526</v>
+      </c>
       <c r="Q39" s="11"/>
       <c r="R39" s="11"/>
       <c r="S39" s="11"/>
       <c r="T39" s="11"/>
       <c r="U39" s="11">
-        <f t="shared" ref="U39:AR39" si="39">+U15/T15-1</f>
+        <f t="shared" ref="U39:AR39" si="40">+U15/T15-1</f>
         <v>0.96329555012616663</v>
       </c>
       <c r="V39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.86255685032858942</v>
       </c>
       <c r="W39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.39429531549043384</v>
       </c>
       <c r="X39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-4.5302121504288917E-2</v>
       </c>
       <c r="Y39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.10262953627235039</v>
       </c>
       <c r="Z39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.18191442628056365</v>
       </c>
       <c r="AA39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.29174045234073365</v>
       </c>
       <c r="AB39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.33534238951032824</v>
       </c>
       <c r="AC39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-0.16423230661857646</v>
       </c>
       <c r="AD39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-2.8735197565797566E-2</v>
       </c>
       <c r="AE39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>6.5193923242380381E-2</v>
       </c>
       <c r="AF39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.12830407960468571</v>
       </c>
       <c r="AG39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.0593782282331041E-2</v>
       </c>
       <c r="AH39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-3.5082575203397748E-2</v>
       </c>
       <c r="AI39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.13365617433414045</v>
       </c>
       <c r="AJ39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>7.0055531824006811E-2</v>
       </c>
       <c r="AK39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.37924151696606789</v>
       </c>
       <c r="AL39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.40578871201157751</v>
       </c>
       <c r="AM39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>-5.5178093473337464E-2</v>
       </c>
       <c r="AN39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.18958378731749836</v>
       </c>
       <c r="AO39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.52729437625938824</v>
       </c>
       <c r="AP39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>0.61397301349325328</v>
       </c>
       <c r="AQ39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>2.2665626277262874E-3</v>
       </c>
       <c r="AR39" s="11">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.2585452658115224</v>
       </c>
       <c r="AS39" s="11">
@@ -5709,167 +5821,170 @@
         <v>35</v>
       </c>
       <c r="C40" s="9">
-        <f t="shared" ref="C40:G40" si="40">C17/C15</f>
+        <f t="shared" ref="C40:G40" si="41">C17/C15</f>
         <v>0.64627363737486099</v>
       </c>
       <c r="D40" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.7005256533649219</v>
       </c>
       <c r="E40" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.73951434878587197</v>
       </c>
       <c r="F40" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.75967063294575399</v>
       </c>
       <c r="G40" s="9">
-        <f t="shared" si="40"/>
+        <f t="shared" si="41"/>
         <v>0.78352019659038552</v>
       </c>
       <c r="H40" s="9">
-        <f t="shared" ref="H40:J40" si="41">H17/H15</f>
+        <f t="shared" ref="H40:J40" si="42">H17/H15</f>
         <v>0.75146471371504664</v>
       </c>
       <c r="I40" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.74556752750698363</v>
       </c>
       <c r="J40" s="9">
-        <f t="shared" si="41"/>
+        <f t="shared" si="42"/>
         <v>0.73026365970862683</v>
       </c>
       <c r="K40" s="9">
-        <f t="shared" ref="K40:L40" si="42">K17/K15</f>
+        <f t="shared" ref="K40:L40" si="43">K17/K15</f>
         <v>0.60523807362353044</v>
       </c>
       <c r="L40" s="9">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v>0.72423678411740799</v>
       </c>
       <c r="M40" s="9">
-        <f t="shared" ref="M40:N40" si="43">M17/M15</f>
+        <f t="shared" ref="M40:N40" si="44">M17/M15</f>
         <v>0.7341157071185489</v>
       </c>
       <c r="N40" s="9">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v>0.74996697344665109</v>
       </c>
       <c r="O40" s="9">
-        <f t="shared" ref="O40" si="44">O17/O15</f>
+        <f t="shared" ref="O40:P40" si="45">O17/O15</f>
         <v>0.74933529375727503</v>
       </c>
-      <c r="P40" s="9"/>
+      <c r="P40" s="9">
+        <f t="shared" si="45"/>
+        <v>0.74975317238440675</v>
+      </c>
       <c r="Q40" s="9"/>
       <c r="R40" s="9"/>
       <c r="S40" s="9"/>
       <c r="T40" s="9">
-        <f t="shared" ref="T40:AS40" si="45">T17/T15</f>
+        <f t="shared" ref="T40:AS40" si="46">T17/T15</f>
         <v>0.62125205270957662</v>
       </c>
       <c r="U40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.62886935848892367</v>
       </c>
       <c r="V40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.6208477580029077</v>
       </c>
       <c r="W40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.30489246362952205</v>
       </c>
       <c r="X40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.29012285066197824</v>
       </c>
       <c r="Y40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.3231220581950644</v>
       </c>
       <c r="Z40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.38306098404377342</v>
       </c>
       <c r="AA40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.42376866830402143</v>
       </c>
       <c r="AB40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.45616004451103742</v>
       </c>
       <c r="AC40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.34286637785672341</v>
       </c>
       <c r="AD40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.35380804432359475</v>
       </c>
       <c r="AE40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.39767629636591112</v>
       </c>
       <c r="AF40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.51439544964519135</v>
       </c>
       <c r="AG40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.52015427464260089</v>
       </c>
       <c r="AH40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.54915254237288136</v>
       </c>
       <c r="AI40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.55510465612985904</v>
       </c>
       <c r="AJ40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.56107784431137719</v>
       </c>
       <c r="AK40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.58798842257597683</v>
       </c>
       <c r="AL40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.59934115709285563</v>
       </c>
       <c r="AM40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.50479407278274135</v>
       </c>
       <c r="AN40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.61989375343469499</v>
       </c>
       <c r="AO40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.62344827586206897</v>
       </c>
       <c r="AP40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.64924014416824583</v>
       </c>
       <c r="AQ40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.56928894490991322</v>
       </c>
       <c r="AR40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.72717573290436954</v>
       </c>
       <c r="AS40" s="9">
-        <f t="shared" si="45"/>
+        <f t="shared" si="46"/>
         <v>0.74988697058169917</v>
       </c>
       <c r="AT40" s="9">
-        <f t="shared" ref="AT40" si="46">AT17/AT15</f>
+        <f t="shared" ref="AT40" si="47">AT17/AT15</f>
         <v>0.71068084357547079</v>
       </c>
       <c r="AU40" s="6"/>
@@ -5931,167 +6046,170 @@
         <v>36</v>
       </c>
       <c r="C41" s="9">
-        <f t="shared" ref="C41:G41" si="47">C21/C15</f>
+        <f t="shared" ref="C41:G41" si="48">C21/C15</f>
         <v>0.29755283648498332</v>
       </c>
       <c r="D41" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.50344265936181243</v>
       </c>
       <c r="E41" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.5748896247240618</v>
       </c>
       <c r="F41" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.61597973125820027</v>
       </c>
       <c r="G41" s="9">
-        <f t="shared" si="47"/>
+        <f t="shared" si="48"/>
         <v>0.64924742743050223</v>
       </c>
       <c r="H41" s="9">
-        <f t="shared" ref="H41:J41" si="48">H21/H15</f>
+        <f t="shared" ref="H41:J41" si="49">H21/H15</f>
         <v>0.62057256990679099</v>
       </c>
       <c r="I41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.62336810900176731</v>
       </c>
       <c r="J41" s="9">
-        <f t="shared" si="48"/>
+        <f t="shared" si="49"/>
         <v>0.61104472299204193</v>
       </c>
       <c r="K41" s="9">
-        <f t="shared" ref="K41:L41" si="49">K21/K15</f>
+        <f t="shared" ref="K41:L41" si="50">K21/K15</f>
         <v>0.49108074985248057</v>
       </c>
       <c r="L41" s="9">
-        <f t="shared" si="49"/>
+        <f t="shared" si="50"/>
         <v>0.60843334830883766</v>
       </c>
       <c r="M41" s="9">
-        <f t="shared" ref="M41:N41" si="50">M21/M15</f>
+        <f t="shared" ref="M41:N41" si="51">M21/M15</f>
         <v>0.63168789250254365</v>
       </c>
       <c r="N41" s="9">
-        <f t="shared" si="50"/>
+        <f t="shared" si="51"/>
         <v>0.65024146080115075</v>
       </c>
       <c r="O41" s="9">
-        <f t="shared" ref="O41" si="51">O21/O15</f>
+        <f t="shared" ref="O41:P41" si="52">O21/O15</f>
         <v>0.65595785088525393</v>
       </c>
-      <c r="P41" s="9"/>
+      <c r="P41" s="9">
+        <f t="shared" si="52"/>
+        <v>0.66237100009353467</v>
+      </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
       <c r="S41" s="9"/>
       <c r="T41" s="9">
-        <f t="shared" ref="T41:AS41" si="52">T21/T15</f>
+        <f t="shared" ref="T41:AS41" si="53">T21/T15</f>
         <v>0.62125205270957662</v>
       </c>
       <c r="U41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.62886935848892367</v>
       </c>
       <c r="V41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.6208477580029077</v>
       </c>
       <c r="W41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.10778932329622133</v>
       </c>
       <c r="X41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.1376755744139253E-2</v>
       </c>
       <c r="Y41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.651300252284408E-2</v>
       </c>
       <c r="Z41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.14767181030160956</v>
       </c>
       <c r="AA41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.14776338801428987</v>
       </c>
       <c r="AB41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.20409335604437434</v>
       </c>
       <c r="AC41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-1.2798191108013595E-2</v>
       </c>
       <c r="AD41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>-2.9744967976322981E-2</v>
       </c>
       <c r="AE41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>5.6090789710973574E-2</v>
       </c>
       <c r="AF41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1621586671102295</v>
       </c>
       <c r="AG41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.15145208390622875</v>
       </c>
       <c r="AH41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.12009685230024213</v>
       </c>
       <c r="AI41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.16211020931225972</v>
       </c>
       <c r="AJ41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.17524950099800399</v>
       </c>
       <c r="AK41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.28031837916063673</v>
       </c>
       <c r="AL41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.33045089561457691</v>
       </c>
       <c r="AM41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.13793854870342123</v>
       </c>
       <c r="AN41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.2606704524638212</v>
       </c>
       <c r="AO41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.27178410794602698</v>
       </c>
       <c r="AP41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.37305391446512837</v>
       </c>
       <c r="AQ41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.1565952398606065</v>
       </c>
       <c r="AR41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.54121663766783756</v>
       </c>
       <c r="AS41" s="9">
-        <f t="shared" si="52"/>
+        <f t="shared" si="53"/>
         <v>0.62417526839697468</v>
       </c>
       <c r="AT41" s="9">
-        <f t="shared" ref="AT41" si="53">AT21/AT15</f>
+        <f t="shared" ref="AT41" si="54">AT21/AT15</f>
         <v>0.60381683631412719</v>
       </c>
       <c r="AU41" s="6"/>
@@ -6153,167 +6271,170 @@
         <v>37</v>
       </c>
       <c r="C42" s="9">
-        <f t="shared" ref="C42:G42" si="54">C26/C25</f>
+        <f t="shared" ref="C42:G42" si="55">C26/C25</f>
         <v>7.5147125396106837E-2</v>
       </c>
       <c r="D42" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.11359404096834265</v>
       </c>
       <c r="E42" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.12155483748336818</v>
       </c>
       <c r="F42" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.12902311073302142</v>
       </c>
       <c r="G42" s="9">
-        <f t="shared" si="54"/>
+        <f t="shared" si="55"/>
         <v>0.13878117946640431</v>
       </c>
       <c r="H42" s="9">
-        <f t="shared" ref="H42:J42" si="55">H26/H25</f>
+        <f t="shared" ref="H42:J42" si="56">H26/H25</f>
         <v>0.1360986780472572</v>
       </c>
       <c r="I42" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.13474637031726117</v>
       </c>
       <c r="J42" s="9">
-        <f t="shared" si="55"/>
+        <f t="shared" si="56"/>
         <v>0.1239639925447119</v>
       </c>
       <c r="K42" s="9">
-        <f t="shared" ref="K42:L42" si="56">K26/K25</f>
+        <f t="shared" ref="K42:L42" si="57">K26/K25</f>
         <v>0.1430853491556367</v>
       </c>
       <c r="L42" s="9">
-        <f t="shared" si="56"/>
+        <f t="shared" si="57"/>
         <v>0.15330385182336731</v>
       </c>
       <c r="M42" s="9">
-        <f t="shared" ref="M42:N42" si="57">M26/M25</f>
+        <f t="shared" ref="M42:N42" si="58">M26/M25</f>
         <v>0.15884647827920709</v>
       </c>
       <c r="N42" s="9">
-        <f t="shared" si="57"/>
+        <f t="shared" si="58"/>
         <v>0.14756830763735937</v>
       </c>
       <c r="O42" s="9">
-        <f t="shared" ref="O42" si="58">O26/O25</f>
+        <f t="shared" ref="O42:P42" si="59">O26/O25</f>
         <v>0.16568673733602277</v>
       </c>
-      <c r="P42" s="9"/>
+      <c r="P42" s="9">
+        <f t="shared" si="59"/>
+        <v>0.16528451759967555</v>
+      </c>
       <c r="Q42" s="9"/>
       <c r="R42" s="9"/>
       <c r="S42" s="9"/>
       <c r="T42" s="9">
-        <f t="shared" ref="T42:AS42" si="59">T26/T25</f>
+        <f t="shared" ref="T42:AS42" si="60">T26/T25</f>
         <v>5.9138414478715267E-3</v>
       </c>
       <c r="U42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.9407382012947518E-3</v>
       </c>
       <c r="V42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.9356954041987374E-3</v>
       </c>
       <c r="W42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.9655298689946044E-3</v>
       </c>
       <c r="X42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.8020887519507061E-3</v>
       </c>
       <c r="Y42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>5.7042211236314954E-3</v>
       </c>
       <c r="Z42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.9625967053699188E-3</v>
       </c>
       <c r="AA42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.692944431326599E-3</v>
       </c>
       <c r="AB42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.643789549764788E-3</v>
       </c>
       <c r="AC42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0</v>
       </c>
       <c r="AD42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.8462349993406376E-3</v>
       </c>
       <c r="AE42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.6824202379859894E-3</v>
       </c>
       <c r="AF42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.6176495895644401E-3</v>
       </c>
       <c r="AG42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.5998976065531808E-3</v>
       </c>
       <c r="AH42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.6818181818181819E-3</v>
       </c>
       <c r="AI42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.7719568567026193E-3</v>
       </c>
       <c r="AJ42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.7583892617449666E-3</v>
       </c>
       <c r="AK42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.5398442180946674E-3</v>
       </c>
       <c r="AL42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>1.5818838201509683E-3</v>
       </c>
       <c r="AM42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.1359950093574549E-3</v>
       </c>
       <c r="AN42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>4.0414878397711013E-4</v>
       </c>
       <c r="AO42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.9935364727608497E-4</v>
       </c>
       <c r="AP42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>3.9479081214109928E-4</v>
       </c>
       <c r="AQ42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>-4.4726142071274816E-2</v>
       </c>
       <c r="AR42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.1199952687917677</v>
       </c>
       <c r="AS42" s="9">
-        <f t="shared" si="59"/>
+        <f t="shared" si="60"/>
         <v>0.13264941803727417</v>
       </c>
       <c r="AT42" s="9">
-        <f t="shared" ref="AT42" si="60">AT26/AT25</f>
+        <f t="shared" ref="AT42" si="61">AT26/AT25</f>
         <v>0.15117002474372571</v>
       </c>
       <c r="AU42" s="6"/>
@@ -7212,39 +7333,39 @@
         <v>97</v>
       </c>
       <c r="C50" s="4">
-        <f t="shared" ref="C50:K50" si="61">+SUM(C45:C49)</f>
+        <f t="shared" ref="C50:K50" si="62">+SUM(C45:C49)</f>
         <v>0</v>
       </c>
       <c r="D50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="H50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="I50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="K50" s="4">
-        <f t="shared" si="61"/>
+        <f t="shared" si="62"/>
         <v>0</v>
       </c>
       <c r="L50" s="4">
@@ -8239,39 +8360,39 @@
         <v>98</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" ref="C58:K58" si="62">+C57+C50</f>
+        <f t="shared" ref="C58:K58" si="63">+C57+C50</f>
         <v>0</v>
       </c>
       <c r="D58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="E58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="F58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="G58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="H58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="I58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="J58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K58" s="8">
-        <f t="shared" si="62"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L58" s="8">
@@ -9309,7 +9430,7 @@
       <c r="AQ66" s="4"/>
       <c r="AR66" s="4"/>
       <c r="AS66" s="4">
-        <f t="shared" ref="AS66" si="63">+SUM(AS63:AS65)</f>
+        <f t="shared" ref="AS66" si="64">+SUM(AS63:AS65)</f>
         <v>14227</v>
       </c>
       <c r="AT66" s="4">
@@ -9515,39 +9636,39 @@
         <v>106</v>
       </c>
       <c r="C68" s="8">
-        <f t="shared" ref="C68:K68" si="64">+C67+C66+C62</f>
+        <f t="shared" ref="C68:K68" si="65">+C67+C66+C62</f>
         <v>0</v>
       </c>
       <c r="D68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="E68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="F68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="G68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="H68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="I68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="J68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="K68" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="65"/>
         <v>0</v>
       </c>
       <c r="L68" s="8">
@@ -9587,7 +9708,7 @@
       <c r="AQ68" s="8"/>
       <c r="AR68" s="8"/>
       <c r="AS68" s="8">
-        <f t="shared" ref="AS68" si="65">+AS67+AS66+AS62</f>
+        <f t="shared" ref="AS68" si="66">+AS67+AS66+AS62</f>
         <v>111601</v>
       </c>
       <c r="AT68" s="8">
@@ -9825,11 +9946,11 @@
       <c r="AP70" s="4"/>
       <c r="AQ70" s="4"/>
       <c r="AR70" s="4">
-        <f t="shared" ref="AR70:AS70" si="66">+AR27</f>
+        <f t="shared" ref="AR70:AS70" si="67">+AR27</f>
         <v>29760</v>
       </c>
       <c r="AS70" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="67"/>
         <v>72880</v>
       </c>
       <c r="AT70" s="4">
@@ -11314,19 +11435,19 @@
       <c r="AN82" s="4"/>
       <c r="AO82" s="4"/>
       <c r="AP82" s="4">
-        <f t="shared" ref="AP82" si="67">+SUM(AP76:AP81)</f>
+        <f t="shared" ref="AP82" si="68">+SUM(AP76:AP81)</f>
         <v>0</v>
       </c>
       <c r="AQ82" s="4">
-        <f t="shared" ref="AQ82" si="68">+SUM(AQ76:AQ81)</f>
+        <f t="shared" ref="AQ82" si="69">+SUM(AQ76:AQ81)</f>
         <v>0</v>
       </c>
       <c r="AR82" s="4">
-        <f t="shared" ref="AR82:AS82" si="69">+SUM(AR76:AR81)</f>
+        <f t="shared" ref="AR82:AS82" si="70">+SUM(AR76:AR81)</f>
         <v>-3722</v>
       </c>
       <c r="AS82" s="4">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>-9383</v>
       </c>
       <c r="AT82" s="4">
@@ -11447,19 +11568,19 @@
       <c r="AN83" s="4"/>
       <c r="AO83" s="4"/>
       <c r="AP83" s="8">
-        <f t="shared" ref="AP83" si="70">+SUM(AP70:AP75)+AP82</f>
+        <f t="shared" ref="AP83" si="71">+SUM(AP70:AP75)+AP82</f>
         <v>0</v>
       </c>
       <c r="AQ83" s="8">
-        <f t="shared" ref="AQ83" si="71">+SUM(AQ70:AQ75)+AQ82</f>
+        <f t="shared" ref="AQ83" si="72">+SUM(AQ70:AQ75)+AQ82</f>
         <v>0</v>
       </c>
       <c r="AR83" s="8">
-        <f t="shared" ref="AR83:AS83" si="72">+SUM(AR70:AR75)+AR82</f>
+        <f t="shared" ref="AR83:AS83" si="73">+SUM(AR70:AR75)+AR82</f>
         <v>28090</v>
       </c>
       <c r="AS83" s="8">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>64089</v>
       </c>
       <c r="AT83" s="8">
@@ -12454,19 +12575,19 @@
       <c r="AN91" s="4"/>
       <c r="AO91" s="4"/>
       <c r="AP91" s="8">
-        <f t="shared" ref="AP91" si="73">+SUM(AP84:AP90)</f>
+        <f t="shared" ref="AP91" si="74">+SUM(AP84:AP90)</f>
         <v>0</v>
       </c>
       <c r="AQ91" s="8">
-        <f t="shared" ref="AQ91" si="74">+SUM(AQ84:AQ90)</f>
+        <f t="shared" ref="AQ91" si="75">+SUM(AQ84:AQ90)</f>
         <v>0</v>
       </c>
       <c r="AR91" s="8">
-        <f t="shared" ref="AR91" si="75">+SUM(AR84:AR90)</f>
+        <f t="shared" ref="AR91" si="76">+SUM(AR84:AR90)</f>
         <v>-10566</v>
       </c>
       <c r="AS91" s="8">
-        <f t="shared" ref="AS91" si="76">+SUM(AS84:AS90)</f>
+        <f t="shared" ref="AS91" si="77">+SUM(AS84:AS90)</f>
         <v>-20421</v>
       </c>
       <c r="AT91" s="8">
